--- a/第5回_Multi-Head_Attention/excel_multi_head_attention_demo.xlsx
+++ b/第5回_Multi-Head_Attention/excel_multi_head_attention_demo.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="00_README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="01_INPUT_X" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="02_WEIGHTS_HEAD1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="03_QKV_HEAD1" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="04_SCORE_HEAD1" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="05_SOFTMAX_HEAD1" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="06_OUTPUT_HEAD1" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="07_WEIGHTS_HEAD2" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="08_QKV_HEAD2" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="09_SCORE_HEAD2" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="10_SOFTMAX_HEAD2" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="11_OUTPUT_HEAD2" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="12_CONCAT" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="13_FOCUS_TRACE" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="14_RUN_PYTHON" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="15_TROUBLE" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="16_SERIES_ROADMAP" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_INPUT_X" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_WEIGHTS_HEAD1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_QKV_HEAD1" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_SCORE_HEAD1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_SOFTMAX_HEAD1" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_OUTPUT_HEAD1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_WEIGHTS_HEAD2" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_QKV_HEAD2" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_SCORE_HEAD2" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_SOFTMAX_HEAD2" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_OUTPUT_HEAD2" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_CONCAT" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_FOCUS_TRACE" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_RUN_PYTHON" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_TROUBLE" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_SERIES_ROADMAP" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'00_README'!$A$3:$B$9</definedName>
